--- a/data/2nd Round/Corrected/Mo_125Se_200Sb_Results Table.xlsx
+++ b/data/2nd Round/Corrected/Mo_125Se_200Sb_Results Table.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Corrected Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -507,6 +506,16 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Rseriescm2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Rshuntcm2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -526,10 +535,6 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>9.177846000000001</v>
       </c>
@@ -539,9 +544,6 @@
       <c r="L2" t="n">
         <v>1.09e-06</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>14.575</v>
       </c>
@@ -555,6 +557,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S2" t="n">
+        <v>0.4964651479757268</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.5667955008713008</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -595,9 +603,6 @@
       <c r="L3" t="n">
         <v>1.164e-05</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>14.741</v>
       </c>
@@ -611,6 +616,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S3" t="n">
+        <v>2.104972849468559</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.172511907948603</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -651,9 +662,6 @@
       <c r="L4" t="n">
         <v>1.926e-05</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>14.576</v>
       </c>
@@ -667,6 +675,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S4" t="n">
+        <v>3.211668892742049</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.721736472363225</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -686,10 +700,6 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>12.544798</v>
       </c>
@@ -699,9 +709,6 @@
       <c r="L5" t="n">
         <v>3.09e-06</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>14.556</v>
       </c>
@@ -715,6 +722,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S5" t="n">
+        <v>1.028490193396607</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.388586600243251</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -755,9 +768,6 @@
       <c r="L6" t="n">
         <v>3.036e-05</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>14.58</v>
       </c>
@@ -771,6 +781,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S6" t="n">
+        <v>3.518421557704881</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.736752493627184</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -811,9 +827,6 @@
       <c r="L7" t="n">
         <v>0.00019305</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>14.831</v>
       </c>
@@ -827,6 +840,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S7" t="n">
+        <v>5.955249519281138</v>
+      </c>
+      <c r="T7" t="n">
+        <v>16.0796925691705</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -867,9 +886,6 @@
       <c r="L8" t="n">
         <v>0.00013138</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>14.553</v>
       </c>
@@ -883,6 +899,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S8" t="n">
+        <v>6.858299234573748</v>
+      </c>
+      <c r="T8" t="n">
+        <v>12.91454697096439</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -902,10 +924,6 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>9.00295</v>
       </c>
@@ -915,9 +933,6 @@
       <c r="L9" t="n">
         <v>2.34e-06</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>14.307</v>
       </c>
@@ -931,6 +946,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S9" t="n">
+        <v>0.7381120090414142</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.9399645875696092</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -971,9 +992,6 @@
       <c r="L10" t="n">
         <v>0.00011995</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>14.831</v>
       </c>
@@ -987,6 +1005,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S10" t="n">
+        <v>6.68176598777722</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9.960435041697002</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1027,9 +1051,6 @@
       <c r="L11" t="n">
         <v>0.00024815</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>14.561</v>
       </c>
@@ -1043,6 +1064,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S11" t="n">
+        <v>6.692911458965582</v>
+      </c>
+      <c r="T11" t="n">
+        <v>19.72045904196387</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1083,9 +1110,6 @@
       <c r="L12" t="n">
         <v>5.077e-05</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>14.556</v>
       </c>
@@ -1099,7 +1123,14 @@
           <t>08/21/2026</t>
         </is>
       </c>
-    </row>
+      <c r="S12" t="n">
+        <v>3.763801251439972</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6.882080445269805</v>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
